--- a/etf_holdings/2026-09-24_errors.xlsx
+++ b/etf_holdings/2026-09-24_errors.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:38:09</t>
+          <t>2026-09-24 21:46:59</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-24 21:38:17</t>
+          <t>2026-09-24 21:47:06</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -485,196 +485,174 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00980A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-24 21:38:24</t>
+          <t>2026-09-24 21:47:25</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00980A 未抓到任何持股資料</t>
+          <t>00982A 未抓到任何持股資料</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-24 21:38:33</t>
+          <t>2026-09-24 21:47:33</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00982A 未抓到任何持股資料</t>
+          <t>00403A 未抓到任何持股資料</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-24 21:38:39</t>
+          <t>2026-09-24 21:47:40</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00403A 未抓到任何持股資料</t>
+          <t>00985A 未抓到任何持股資料</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-24 21:38:47</t>
+          <t>2026-09-24 21:47:49</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00985A 未抓到任何持股資料</t>
+          <t>00992A 未抓到任何持股資料</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-24 21:38:53</t>
+          <t>2026-09-24 21:47:57</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00992A 未抓到任何持股資料</t>
+          <t>00990A 未抓到任何持股資料</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00405A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:02</t>
+          <t>2026-09-24 21:48:05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00990A 未抓到任何持股資料</t>
+          <t>00405A 未抓到任何持股資料</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00405A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00407A/holdings</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:10</t>
+          <t>2026-09-24 21:48:12</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>00405A 未抓到任何持股資料</t>
+          <t>00407A 未抓到任何持股資料</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00407A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-24 21:39:18</t>
+          <t>2026-09-24 21:48:19</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
-        <is>
-          <t>00407A 未抓到任何持股資料</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2026-09-24 21:39:27</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
         <is>
           <t>00993A 未抓到任何持股資料</t>
         </is>

--- a/etf_holdings/2026-09-24_errors.xlsx
+++ b/etf_holdings/2026-09-24_errors.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,220 +441,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:46:59</t>
+          <t>2026-09-24 22:14:20</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00981A 未抓到任何持股資料</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>00991A</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-09-24 21:47:06</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>00991A 未抓到任何持股資料</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>00982A</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-09-24 21:47:25</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>00982A 未抓到任何持股資料</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-09-24 21:47:33</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>00403A 未抓到任何持股資料</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-09-24 21:47:40</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>00985A 未抓到任何持股資料</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-09-24 21:47:49</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>00992A 未抓到任何持股資料</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-09-24 21:47:57</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>00990A 未抓到任何持股資料</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>00405A</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-09-24 21:48:05</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>00405A 未抓到任何持股資料</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00407A/holdings</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2026-09-24 21:48:12</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>00407A 未抓到任何持股資料</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2026-09-24 21:48:19</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>00993A 未抓到任何持股資料</t>
+          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
+Call log:
+  - navigating to "https://www.etfinfo.tw/etf/00990A/holdings", waiting until "networkidle"
+</t>
         </is>
       </c>
     </row>
